--- a/templates/time-upload.xlsx
+++ b/templates/time-upload.xlsx
@@ -13,7 +13,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
